--- a/Team-Data/2012-13/2-2-2012-13.xlsx
+++ b/Team-Data/2012-13/2-2-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,91 +728,91 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
         <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.578</v>
       </c>
       <c r="H2" t="n">
         <v>48.7</v>
       </c>
       <c r="I2" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J2" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.46</v>
       </c>
       <c r="L2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O2" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.696</v>
+        <v>0.698</v>
       </c>
       <c r="R2" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U2" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="V2" t="n">
         <v>15.1</v>
       </c>
       <c r="W2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y2" t="n">
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.2</v>
+        <v>96.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -754,13 +821,13 @@
         <v>7</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -793,10 +860,10 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
@@ -805,13 +872,13 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-0.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
         <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -942,7 +1009,7 @@
         <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL3" t="n">
         <v>28</v>
@@ -960,7 +1027,7 @@
         <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
@@ -972,10 +1039,10 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF4" t="n">
         <v>10</v>
@@ -1115,7 +1182,7 @@
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>10</v>
@@ -1133,7 +1200,7 @@
         <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
@@ -1148,13 +1215,13 @@
         <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
         <v>18</v>
       </c>
       <c r="AU4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
         <v>9</v>
@@ -1163,7 +1230,7 @@
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>5</v>
@@ -1172,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
         <v>13</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.239</v>
+        <v>0.244</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I5" t="n">
         <v>34.6</v>
       </c>
       <c r="J5" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>0.424</v>
@@ -1234,28 +1301,28 @@
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O5" t="n">
         <v>19.6</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.754</v>
+        <v>0.751</v>
       </c>
       <c r="R5" t="n">
         <v>11.5</v>
       </c>
       <c r="S5" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T5" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U5" t="n">
         <v>18.8</v>
@@ -1264,7 +1331,7 @@
         <v>14.4</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
         <v>6.4</v>
@@ -1273,25 +1340,25 @@
         <v>7.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB5" t="n">
         <v>94.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.5</v>
+        <v>-8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG5" t="n">
         <v>29</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1324,16 +1391,16 @@
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
@@ -1342,7 +1409,7 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
         <v>5</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -1389,88 +1456,88 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>0.617</v>
+        <v>0.609</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J6" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M6" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O6" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P6" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R6" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U6" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y6" t="n">
         <v>5.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
         <v>93.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
         <v>8</v>
@@ -1479,13 +1546,13 @@
         <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
@@ -1497,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1506,7 +1573,7 @@
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
         <v>8</v>
@@ -1515,25 +1582,25 @@
         <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -1571,46 +1638,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
         <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>0.292</v>
+        <v>0.277</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="J7" t="n">
-        <v>84.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M7" t="n">
         <v>20.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.351</v>
+        <v>0.348</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P7" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.759</v>
+        <v>0.756</v>
       </c>
       <c r="R7" t="n">
         <v>12.8</v>
@@ -1619,13 +1686,13 @@
         <v>28.5</v>
       </c>
       <c r="T7" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U7" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="V7" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W7" t="n">
         <v>8.1</v>
@@ -1634,25 +1701,25 @@
         <v>3.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA7" t="n">
         <v>20.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>96</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.2</v>
+        <v>-5.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
         <v>28</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1679,10 +1746,10 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP7" t="n">
         <v>14</v>
@@ -1697,13 +1764,13 @@
         <v>29</v>
       </c>
       <c r="AT7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
         <v>28</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1888,7 +1955,7 @@
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -1903,10 +1970,10 @@
         <v>22</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2025,7 +2092,7 @@
         <v>8</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2040,7 +2107,7 @@
         <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN9" t="n">
         <v>27</v>
@@ -2079,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,19 +2274,19 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
         <v>26</v>
@@ -2249,7 +2316,7 @@
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>28</v>
@@ -2261,16 +2328,16 @@
         <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
         <v>17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.638</v>
+        <v>0.63</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="K11" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L11" t="n">
         <v>7.9</v>
@@ -2329,16 +2396,16 @@
         <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="O11" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
         <v>21.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.803</v>
+        <v>0.805</v>
       </c>
       <c r="R11" t="n">
         <v>10.9</v>
@@ -2350,37 +2417,37 @@
         <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA11" t="n">
         <v>19.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
@@ -2389,10 +2456,10 @@
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>8</v>
@@ -2440,7 +2507,7 @@
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
@@ -2452,7 +2519,7 @@
         <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -2481,64 +2548,64 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
         <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.531</v>
+        <v>0.521</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
         <v>82.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L12" t="n">
         <v>10.1</v>
       </c>
       <c r="M12" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="N12" t="n">
         <v>0.359</v>
       </c>
       <c r="O12" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P12" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0.754</v>
       </c>
       <c r="R12" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S12" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U12" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V12" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W12" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>4.1</v>
@@ -2553,16 +2620,16 @@
         <v>19.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.1</v>
+        <v>105</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
         <v>15</v>
@@ -2577,10 +2644,10 @@
         <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF13" t="n">
         <v>10</v>
@@ -2753,13 +2820,13 @@
         <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2792,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2804,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
         <v>14</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2938,16 +3005,16 @@
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM14" t="n">
         <v>12</v>
@@ -2959,7 +3026,7 @@
         <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>26</v>
@@ -2968,7 +3035,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
@@ -2989,7 +3056,7 @@
         <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3120,13 +3187,13 @@
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
         <v>20</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3162,10 +3229,10 @@
         <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
@@ -3180,7 +3247,7 @@
         <v>5</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3305,10 +3372,10 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3350,10 +3417,10 @@
         <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>5.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3514,7 +3581,7 @@
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3526,7 +3593,7 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -3573,34 +3640,34 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
         <v>21</v>
       </c>
       <c r="G18" t="n">
-        <v>0.543</v>
+        <v>0.533</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J18" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L18" t="n">
         <v>6.6</v>
       </c>
       <c r="M18" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="N18" t="n">
         <v>0.355</v>
@@ -3624,10 +3691,10 @@
         <v>43.7</v>
       </c>
       <c r="U18" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V18" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W18" t="n">
         <v>8.4</v>
@@ -3642,16 +3709,16 @@
         <v>19.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.7</v>
+        <v>97.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3660,7 +3727,7 @@
         <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
         <v>25</v>
@@ -3672,13 +3739,13 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="n">
         <v>14</v>
@@ -3690,19 +3757,19 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
         <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>8</v>
@@ -3717,7 +3784,7 @@
         <v>6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -3755,31 +3822,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.409</v>
+        <v>0.395</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.6</v>
+        <v>35.3</v>
       </c>
       <c r="J19" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.435</v>
+        <v>0.432</v>
       </c>
       <c r="L19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M19" t="n">
         <v>18.5</v>
@@ -3791,13 +3858,13 @@
         <v>18.5</v>
       </c>
       <c r="P19" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="R19" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S19" t="n">
         <v>30.7</v>
@@ -3806,13 +3873,13 @@
         <v>43.8</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V19" t="n">
         <v>15.3</v>
       </c>
       <c r="W19" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X19" t="n">
         <v>5.2</v>
@@ -3821,22 +3888,22 @@
         <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
         <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.2</v>
+        <v>94.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-1.7</v>
+        <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
         <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF19" t="n">
         <v>18</v>
@@ -3851,22 +3918,22 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP19" t="n">
         <v>6</v>
@@ -3881,34 +3948,34 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX19" t="n">
         <v>15</v>
       </c>
       <c r="AY19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -3937,85 +4004,85 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" t="n">
-        <v>0.313</v>
+        <v>0.319</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="J20" t="n">
-        <v>80</v>
+        <v>80.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="P20" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
         <v>11.3</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
-        <v>41.2</v>
+        <v>41.5</v>
       </c>
       <c r="U20" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="W20" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="X20" t="n">
         <v>5.3</v>
       </c>
       <c r="Y20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AD20" t="n">
         <v>6</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4027,10 +4094,10 @@
         <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
@@ -4039,7 +4106,7 @@
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM20" t="n">
         <v>19</v>
@@ -4063,13 +4130,13 @@
         <v>21</v>
       </c>
       <c r="AT20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU20" t="n">
         <v>21</v>
       </c>
-      <c r="AU20" t="n">
-        <v>22</v>
-      </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4084,13 +4151,13 @@
         <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -4119,88 +4186,88 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
         <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>0.667</v>
+        <v>0.659</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J21" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L21" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.385</v>
+        <v>0.383</v>
       </c>
       <c r="O21" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="P21" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U21" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="V21" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="W21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y21" t="n">
         <v>3.8</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>3.7</v>
       </c>
       <c r="Z21" t="n">
         <v>19.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>101</v>
+        <v>100.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD21" t="n">
         <v>28</v>
       </c>
       <c r="AE21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF21" t="n">
         <v>5</v>
@@ -4212,13 +4279,13 @@
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4236,25 +4303,25 @@
         <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4263,13 +4330,13 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>18</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC21" t="n">
         <v>5</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
         <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>0.745</v>
+        <v>0.761</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
       </c>
       <c r="I22" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J22" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K22" t="n">
         <v>0.479</v>
@@ -4331,10 +4398,10 @@
         <v>19.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O22" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="P22" t="n">
         <v>27.2</v>
@@ -4343,49 +4410,49 @@
         <v>0.836</v>
       </c>
       <c r="R22" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S22" t="n">
         <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U22" t="n">
         <v>21.8</v>
       </c>
       <c r="V22" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="n">
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.8</v>
+        <v>105.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
         <v>2</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4421,22 +4488,22 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS22" t="n">
         <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4448,13 +4515,13 @@
         <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G23" t="n">
-        <v>0.298</v>
+        <v>0.304</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J23" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="K23" t="n">
         <v>0.454</v>
@@ -4513,43 +4580,43 @@
         <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
         <v>12.5</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.781</v>
+        <v>0.789</v>
       </c>
       <c r="R23" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="S23" t="n">
         <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U23" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="V23" t="n">
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X23" t="n">
         <v>4.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
         <v>16.5</v>
@@ -4558,10 +4625,10 @@
         <v>94.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.5</v>
+        <v>-4.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
         <v>27</v>
@@ -4573,13 +4640,13 @@
         <v>27</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK23" t="n">
         <v>11</v>
@@ -4591,7 +4658,7 @@
         <v>13</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,10 +4667,10 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>9</v>
@@ -4612,10 +4679,10 @@
         <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4624,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
         <v>8</v>
@@ -4633,10 +4700,10 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
@@ -4758,13 +4825,13 @@
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4788,19 +4855,19 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
         <v>22</v>
       </c>
       <c r="AU24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
         <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4868,13 +4935,13 @@
         <v>84.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L25" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M25" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="N25" t="n">
         <v>0.329</v>
@@ -4883,19 +4950,19 @@
         <v>15</v>
       </c>
       <c r="P25" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0.751</v>
       </c>
       <c r="R25" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T25" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U25" t="n">
         <v>22</v>
@@ -4907,7 +4974,7 @@
         <v>7.9</v>
       </c>
       <c r="X25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y25" t="n">
         <v>5.2</v>
@@ -4916,16 +4983,16 @@
         <v>20.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB25" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.4</v>
+        <v>-4.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>25</v>
@@ -4940,13 +5007,13 @@
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
@@ -4964,13 +5031,13 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>17</v>
       </c>
       <c r="AS25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT25" t="n">
         <v>25</v>
@@ -4982,13 +5049,13 @@
         <v>5</v>
       </c>
       <c r="AW25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ25" t="n">
         <v>18</v>
@@ -4997,10 +5064,10 @@
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -5029,55 +5096,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
         <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I26" t="n">
         <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L26" t="n">
         <v>8.1</v>
       </c>
       <c r="M26" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="O26" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P26" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.773</v>
+        <v>0.776</v>
       </c>
       <c r="R26" t="n">
         <v>11.7</v>
       </c>
       <c r="S26" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T26" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U26" t="n">
         <v>21.1</v>
@@ -5086,10 +5153,10 @@
         <v>15</v>
       </c>
       <c r="W26" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
         <v>4</v>
@@ -5098,16 +5165,16 @@
         <v>18.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5125,10 +5192,10 @@
         <v>22</v>
       </c>
       <c r="AJ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO26" t="n">
         <v>18</v>
@@ -5152,22 +5219,22 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV26" t="n">
         <v>19</v>
       </c>
       <c r="AW26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX26" t="n">
         <v>21</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>20</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5179,10 +5246,10 @@
         <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.347</v>
+        <v>0.354</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J27" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K27" t="n">
         <v>0.438</v>
@@ -5238,61 +5305,61 @@
         <v>6.5</v>
       </c>
       <c r="M27" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O27" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P27" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q27" t="n">
         <v>0.753</v>
       </c>
       <c r="R27" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S27" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T27" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="U27" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
         <v>4.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA27" t="n">
         <v>19.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-7.2</v>
+        <v>-6.6</v>
       </c>
       <c r="AD27" t="n">
         <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
@@ -5307,28 +5374,28 @@
         <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>19</v>
       </c>
       <c r="AM27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN27" t="n">
         <v>15</v>
       </c>
       <c r="AO27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -5340,13 +5407,13 @@
         <v>27</v>
       </c>
       <c r="AU27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV27" t="n">
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
@@ -5361,7 +5428,7 @@
         <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.776</v>
+        <v>0.771</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
@@ -5411,34 +5478,34 @@
         <v>39.7</v>
       </c>
       <c r="J28" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.487</v>
       </c>
       <c r="L28" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M28" t="n">
         <v>22.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.379</v>
+        <v>0.382</v>
       </c>
       <c r="O28" t="n">
         <v>16.3</v>
       </c>
       <c r="P28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.788</v>
+        <v>0.786</v>
       </c>
       <c r="R28" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T28" t="n">
         <v>41.5</v>
@@ -5450,22 +5517,22 @@
         <v>15</v>
       </c>
       <c r="W28" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.1</v>
+        <v>104.3</v>
       </c>
       <c r="AC28" t="n">
         <v>8.4</v>
@@ -5510,7 +5577,7 @@
         <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5546,7 +5613,7 @@
         <v>3</v>
       </c>
       <c r="BC28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>-1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
@@ -5668,13 +5735,13 @@
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5683,7 +5750,7 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
         <v>16</v>
@@ -5704,19 +5771,19 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
         <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -5757,67 +5824,67 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" t="n">
         <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>0.542</v>
+        <v>0.553</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J30" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.448</v>
       </c>
       <c r="L30" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M30" t="n">
         <v>17</v>
       </c>
       <c r="N30" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O30" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P30" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R30" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S30" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U30" t="n">
         <v>22.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y30" t="n">
         <v>6.1</v>
@@ -5832,34 +5899,34 @@
         <v>98</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>12</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
         <v>14</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>25</v>
@@ -5868,10 +5935,10 @@
         <v>9</v>
       </c>
       <c r="AO30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
@@ -5880,16 +5947,16 @@
         <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV30" t="n">
         <v>16</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>11</v>
       </c>
       <c r="AW30" t="n">
         <v>8</v>
@@ -5898,13 +5965,13 @@
         <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>27</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
         <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>0.239</v>
+        <v>0.244</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
@@ -5957,73 +6024,73 @@
         <v>34.9</v>
       </c>
       <c r="J31" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.421</v>
+        <v>0.422</v>
       </c>
       <c r="L31" t="n">
         <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="O31" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="P31" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.738</v>
       </c>
       <c r="R31" t="n">
         <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U31" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V31" t="n">
         <v>15.5</v>
       </c>
       <c r="W31" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>90.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5.1</v>
+        <v>-5</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6044,10 +6111,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6056,7 +6123,7 @@
         <v>26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
         <v>18</v>
@@ -6080,13 +6147,13 @@
         <v>22</v>
       </c>
       <c r="AY31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-2-2012-13</t>
+          <t>2013-02-02</t>
         </is>
       </c>
     </row>
